--- a/Jpn_test/doc/テスト結果.xlsx
+++ b/Jpn_test/doc/テスト結果.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ISTEST\Git\Jpn_test\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F4008D-DD8A-430C-81E4-D9A0064E06C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{567FD8BB-EBC1-4C2B-BF15-3A4E96F956A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8520" yWindow="1620" windowWidth="12444" windowHeight="11556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8520" yWindow="804" windowWidth="12444" windowHeight="11556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Jpn_test/doc/テスト結果.xlsx
+++ b/Jpn_test/doc/テスト結果.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ISTEST\Git\Jpn_test\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\j1_eb\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{567FD8BB-EBC1-4C2B-BF15-3A4E96F956A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3E3AE6-2BB9-4E28-9091-897C99B50329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8520" yWindow="804" windowWidth="12444" windowHeight="11556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="121">
   <si>
     <t>CS-01</t>
   </si>
@@ -292,10 +292,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>NG</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>CS句指定なしでも￥使えるか</t>
     <rPh sb="2" eb="3">
       <t>ク</t>
@@ -348,10 +344,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>コンパイルエラー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>CS句＄指定で＄も￥も使えるか</t>
     <rPh sb="2" eb="3">
       <t>ク</t>
@@ -400,6 +392,224 @@
     </rPh>
     <rPh sb="7" eb="8">
       <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Acu</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AcuではOK</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（コンパイルエラー）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト内容</t>
+    <rPh sb="3" eb="5">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部分参照</t>
+    <rPh sb="0" eb="4">
+      <t>ブブンサンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部分参照（エラーチェック）</t>
+    <rPh sb="0" eb="4">
+      <t>ブブンサンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（実行時エラーとならない）</t>
+    <rPh sb="3" eb="6">
+      <t>ジッコウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全角半角混合英数字のあつかい</t>
+    <rPh sb="0" eb="4">
+      <t>ゼンカクハンカク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コンゴウ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>エイスウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（1B→2B変換されない）</t>
+    <rPh sb="8" eb="10">
+      <t>ヘンカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行の継続</t>
+    <rPh sb="0" eb="1">
+      <t>ギョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケイゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行の継続（インラインコメント）</t>
+    <rPh sb="0" eb="1">
+      <t>ギョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケイゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OK(一部＆で対応）</t>
+    <rPh sb="3" eb="5">
+      <t>イチブ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（不一致）</t>
+    <rPh sb="3" eb="6">
+      <t>フイッチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OK（コンパイル時エラーチェックされる）</t>
+    <rPh sb="8" eb="9">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OK（実行時エラーとなる）</t>
+    <rPh sb="3" eb="6">
+      <t>ジッコウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー（＆ないので比較対象外）</t>
+    <rPh sb="7" eb="9">
+      <t>ヒカク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ガイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JUST句</t>
+    <rPh sb="4" eb="5">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JUST句(エラーチェック）</t>
+    <rPh sb="4" eb="5">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（コンパイル時エラーならない）</t>
+    <rPh sb="8" eb="9">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PIC句</t>
+    <rPh sb="3" eb="4">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PIC句(エラーチェック）</t>
+    <rPh sb="3" eb="4">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>USAGE句</t>
+    <rPh sb="5" eb="6">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VALUE句</t>
+    <rPh sb="5" eb="6">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VALUE句（エラーチェック）</t>
+    <rPh sb="5" eb="6">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OK(コンパイルエラーとなった）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG(実行時NB0/組み合わせエラー）</t>
+    <rPh sb="3" eb="6">
+      <t>ジッコウジ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（コンパイル時エラー）</t>
+    <rPh sb="8" eb="9">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG(実行時JUST、SPACE、ALL定数、１B-＞２Bエラー）</t>
+    <rPh sb="3" eb="6">
+      <t>ジッコウジ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>テイスウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -739,8 +949,10 @@
   <cols>
     <col min="1" max="2" width="8.796875" style="1"/>
     <col min="3" max="3" width="15.296875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="35.19921875" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.796875" style="1"/>
+    <col min="4" max="4" width="44.19921875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="50.296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.19921875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="2:6">
@@ -750,8 +962,14 @@
       <c r="C4" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="E4" s="1" t="s">
         <v>82</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="2:6">
@@ -762,9 +980,12 @@
         <v>0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>83</v>
       </c>
     </row>
@@ -776,10 +997,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="2:6">
@@ -790,9 +1014,12 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>83</v>
       </c>
     </row>
@@ -804,13 +1031,13 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="2:6">
@@ -821,13 +1048,13 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="2:6">
@@ -838,9 +1065,12 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>83</v>
       </c>
     </row>
@@ -852,13 +1082,13 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="2:6">
@@ -869,13 +1099,13 @@
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="2:6">
@@ -886,10 +1116,13 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>83</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="2:6">
@@ -899,6 +1132,15 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="D14" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="15" spans="2:6">
       <c r="B15" s="1">
@@ -907,6 +1149,15 @@
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="D15" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="16" spans="2:6">
       <c r="B16" s="1">
@@ -915,112 +1166,238 @@
       <c r="C16" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="2:3">
+      <c r="D16" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
       <c r="B17" s="1">
         <v>13</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="2:3">
+      <c r="D17" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
       <c r="B18" s="1">
         <v>14</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="19" spans="2:3">
+      <c r="D18" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
       <c r="B19" s="1">
         <v>15</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="2:3">
+      <c r="D19" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="1">
         <v>16</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="21" spans="2:3">
+      <c r="D20" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
       <c r="B21" s="1">
         <v>17</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="2:3">
+      <c r="D21" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
       <c r="B22" s="1">
         <v>18</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="23" spans="2:3">
+      <c r="D22" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
       <c r="B23" s="1">
         <v>19</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="2:3">
+      <c r="D23" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
       <c r="B24" s="1">
         <v>20</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="25" spans="2:3">
+      <c r="D24" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
       <c r="B25" s="1">
         <v>21</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="26" spans="2:3">
+      <c r="D25" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
       <c r="B26" s="1">
         <v>22</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="27" spans="2:3">
+      <c r="D26" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="B27" s="1">
         <v>23</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="28" spans="2:3">
+      <c r="D27" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6">
       <c r="B28" s="1">
         <v>24</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="29" spans="2:3">
+      <c r="D28" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
       <c r="B29" s="1">
         <v>25</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="2:3">
+      <c r="D29" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
       <c r="B30" s="1">
         <v>26</v>
       </c>
@@ -1028,7 +1405,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="2:3">
+    <row r="31" spans="2:6">
       <c r="B31" s="1">
         <v>27</v>
       </c>
@@ -1036,7 +1413,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="2:3">
+    <row r="32" spans="2:6">
       <c r="B32" s="1">
         <v>28</v>
       </c>

--- a/Jpn_test/doc/テスト結果.xlsx
+++ b/Jpn_test/doc/テスト結果.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\j1_eb\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3E3AE6-2BB9-4E28-9091-897C99B50329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3E83DC-CA60-4456-9D09-5AF1168CC28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8820" yWindow="1512" windowWidth="14544" windowHeight="10860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="147">
   <si>
     <t>CS-01</t>
   </si>
@@ -103,9 +103,6 @@
   </si>
   <si>
     <t>EX5-1-1A</t>
-  </si>
-  <si>
-    <t>EX5-1-1A_old</t>
   </si>
   <si>
     <t>EX5-1-1B</t>
@@ -611,6 +608,237 @@
     <rPh sb="20" eb="22">
       <t>テイスウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（コンパイル時エラーならない、QUOTESとZEROS比較）</t>
+    <rPh sb="8" eb="9">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ヒカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>条件の比較表チェック（エラーチェック）</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ヒカクヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>条件の比較表チェック（正常系）</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ヒカクヒョウ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>セイジョウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（SPACE、ZEROとの比較一致しない）</t>
+    <rPh sb="15" eb="17">
+      <t>ヒカク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イッチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>条件名</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウケンメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（コンパイル時エラーならない、ZEROS比較）</t>
+    <rPh sb="8" eb="9">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヒカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ACCEPT命令</t>
+    <rPh sb="6" eb="8">
+      <t>メイレイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（PIC N/N/N効かない）</t>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（コンパイルエラーになる）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>INITIALIZE命令(正常系）</t>
+    <rPh sb="10" eb="12">
+      <t>メイレイ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>セイジョウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>INSPECT（正常系）</t>
+    <rPh sb="8" eb="11">
+      <t>セイジョウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>INSPECT（異常系）</t>
+    <rPh sb="8" eb="10">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（一部不一致）</t>
+    <rPh sb="3" eb="5">
+      <t>イチブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>フイッチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（一部コンパイル時エラーならない）</t>
+    <rPh sb="3" eb="5">
+      <t>イチブ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MOVE（正常系）</t>
+    <rPh sb="5" eb="8">
+      <t>セイジョウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MOVE（正常系・異常系）</t>
+    <rPh sb="5" eb="8">
+      <t>セイジョウケイ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>イジョウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（実行時不一致1B-&gt;2B、一部コンパイル時エラーならない）</t>
+    <rPh sb="3" eb="6">
+      <t>ジッコウジ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>フイッチ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イチブ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（実行時不一致PIC N/N/N）</t>
+    <rPh sb="3" eb="6">
+      <t>ジッコウジ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>フイッチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MOVE（異常系）</t>
+    <rPh sb="5" eb="7">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>STRING（正常系）</t>
+    <rPh sb="7" eb="10">
+      <t>セイジョウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>STRING（異常系）</t>
+    <rPh sb="7" eb="10">
+      <t>イジョウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OK（コンパイルエラーとなった）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UNSTRING（正常系）</t>
+    <rPh sb="9" eb="12">
+      <t>セイジョウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UNSTRING（異常系）</t>
+    <rPh sb="9" eb="11">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LENGTH関数</t>
+    <rPh sb="6" eb="8">
+      <t>カンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BYTE-LENGTH関数</t>
+    <rPh sb="11" eb="13">
+      <t>カンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（SYNC）</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -944,7 +1172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B4:F84"/>
+  <dimension ref="B4:F83"/>
   <sheetFormatPr defaultRowHeight="19.8"/>
   <cols>
     <col min="1" max="2" width="8.796875" style="1"/>
@@ -957,19 +1185,19 @@
   <sheetData>
     <row r="4" spans="2:6">
       <c r="B4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="2:6">
@@ -980,13 +1208,13 @@
         <v>0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="2:6">
@@ -997,13 +1225,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="2:6">
@@ -1014,13 +1242,13 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="2:6">
@@ -1031,13 +1259,13 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="2:6">
@@ -1048,13 +1276,13 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="2:6">
@@ -1065,13 +1293,13 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="2:6">
@@ -1082,13 +1310,13 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="2:6">
@@ -1099,13 +1327,13 @@
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="2:6">
@@ -1116,13 +1344,13 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="2:6">
@@ -1133,13 +1361,13 @@
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="2:6">
@@ -1150,13 +1378,13 @@
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="2:6">
@@ -1167,13 +1395,13 @@
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="2:6">
@@ -1184,13 +1412,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -1201,13 +1429,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="F18" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="2:6">
@@ -1218,13 +1446,13 @@
         <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="2:6">
@@ -1235,13 +1463,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="2:6">
@@ -1252,13 +1480,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="F21" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -1269,13 +1497,13 @@
         <v>17</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="2:6">
@@ -1286,13 +1514,13 @@
         <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="F23" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="2:6">
@@ -1303,13 +1531,13 @@
         <v>19</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="2:6">
@@ -1320,13 +1548,13 @@
         <v>20</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="2:6">
@@ -1337,13 +1565,13 @@
         <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -1354,13 +1582,13 @@
         <v>22</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="2:6">
@@ -1371,13 +1599,13 @@
         <v>23</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="2:6">
@@ -1388,13 +1616,13 @@
         <v>24</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="F29" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -1404,402 +1632,624 @@
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="D30" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="D31" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="33" spans="2:3">
+      <c r="D32" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5">
       <c r="B33" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="34" spans="2:3">
+      <c r="D33" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5">
       <c r="B34" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="35" spans="2:3">
+      <c r="D34" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5">
       <c r="B35" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="36" spans="2:3">
+      <c r="D35" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5">
       <c r="B36" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="37" spans="2:3">
+      <c r="D36" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5">
       <c r="B37" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="38" spans="2:3">
+      <c r="D37" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5">
       <c r="B38" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="39" spans="2:3">
+      <c r="D38" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5">
       <c r="B39" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="40" spans="2:3">
+      <c r="D39" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5">
       <c r="B40" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="41" spans="2:3">
+      <c r="D40" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5">
       <c r="B41" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="42" spans="2:3">
+      <c r="D41" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5">
       <c r="B42" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="43" spans="2:3">
+      <c r="D42" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5">
       <c r="B43" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="44" spans="2:3">
+      <c r="D43" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5">
       <c r="B44" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="45" spans="2:3">
+      <c r="D44" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5">
       <c r="B45" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="46" spans="2:3">
+      <c r="D45" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5">
       <c r="B46" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="47" spans="2:3">
+      <c r="D46" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5">
       <c r="B47" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="48" spans="2:3">
+      <c r="D47" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5">
       <c r="B48" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="49" spans="2:3">
+      <c r="D48" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5">
       <c r="B49" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="50" spans="2:3">
+      <c r="D49" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5">
       <c r="B50" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="51" spans="2:3">
+      <c r="D50" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5">
       <c r="B51" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="52" spans="2:3">
+      <c r="D51" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5">
       <c r="B52" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="53" spans="2:3">
+      <c r="D52" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5">
       <c r="B53" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="54" spans="2:3">
+      <c r="D53" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5">
       <c r="B54" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="55" spans="2:3">
+      <c r="D54" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5">
       <c r="B55" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="56" spans="2:3">
+      <c r="D55" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5">
       <c r="B56" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="57" spans="2:3">
+      <c r="D56" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5">
       <c r="B57" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="58" spans="2:3">
+      <c r="D57" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5">
       <c r="B58" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="59" spans="2:3">
+      <c r="D58" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5">
       <c r="B59" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="60" spans="2:3">
+      <c r="D59" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5">
       <c r="B60" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="61" spans="2:3">
+      <c r="D60" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5">
       <c r="B61" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="62" spans="2:3">
+      <c r="D61" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5">
       <c r="B62" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="63" spans="2:3">
+      <c r="D62" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5">
       <c r="B63" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="64" spans="2:3">
+      <c r="D63" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5">
       <c r="B64" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="65" spans="2:3">
+      <c r="D64" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5">
       <c r="B65" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="66" spans="2:3">
+      <c r="D65" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5">
       <c r="B66" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="67" spans="2:3">
+      <c r="D66" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5">
       <c r="B67" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="68" spans="2:3">
+    <row r="68" spans="2:5">
       <c r="B68" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="69" spans="2:3">
+    <row r="69" spans="2:5">
       <c r="B69" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="70" spans="2:3">
+    <row r="70" spans="2:5">
       <c r="B70" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="71" spans="2:3">
+    <row r="71" spans="2:5">
       <c r="B71" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="72" spans="2:3">
+    <row r="72" spans="2:5">
       <c r="B72" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="73" spans="2:3">
+    <row r="73" spans="2:5">
       <c r="B73" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="74" spans="2:3">
+    <row r="74" spans="2:5">
       <c r="B74" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="2:3">
+    <row r="75" spans="2:5">
       <c r="B75" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="76" spans="2:3">
+    <row r="76" spans="2:5">
       <c r="B76" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="77" spans="2:3">
+    <row r="77" spans="2:5">
       <c r="B77" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="78" spans="2:3">
+    <row r="78" spans="2:5">
       <c r="B78" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="79" spans="2:3">
+    <row r="79" spans="2:5">
       <c r="B79" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="80" spans="2:3">
+    <row r="80" spans="2:5">
       <c r="B80" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>75</v>
@@ -1807,7 +2257,7 @@
     </row>
     <row r="81" spans="2:3">
       <c r="B81" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>76</v>
@@ -1815,7 +2265,7 @@
     </row>
     <row r="82" spans="2:3">
       <c r="B82" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>77</v>
@@ -1823,18 +2273,10 @@
     </row>
     <row r="83" spans="2:3">
       <c r="B83" s="1">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="84" spans="2:3">
-      <c r="B84" s="1">
-        <v>80</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/Jpn_test/doc/テスト結果.xlsx
+++ b/Jpn_test/doc/テスト結果.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\j1_eb\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Acucorp\acutest\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3E83DC-CA60-4456-9D09-5AF1168CC28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E326D36-440C-4F1E-A7F5-78E3A652E2E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8820" yWindow="1512" windowWidth="14544" windowHeight="10860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="153">
   <si>
     <t>CS-01</t>
   </si>
@@ -839,6 +839,54 @@
   </si>
   <si>
     <t>NG（SYNC）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（コンパイル時エラーならない。一部実行時エラー）</t>
+    <rPh sb="8" eb="9">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="17" eb="22">
+      <t>イチブジッコウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（一部実行時エラー）</t>
+    <rPh sb="3" eb="8">
+      <t>イチブジッコウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（一部不一致）</t>
+    <rPh sb="3" eb="8">
+      <t>イチブフイッチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（実行時不一致、一部コンパイル時エラーならない）</t>
+    <rPh sb="3" eb="6">
+      <t>ジッコウジ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>フイッチ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イチブ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG(＆なし）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG(BYTE-LENGTHなし）</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1178,7 +1226,7 @@
     <col min="1" max="2" width="8.796875" style="1"/>
     <col min="3" max="3" width="15.296875" style="1" customWidth="1"/>
     <col min="4" max="4" width="44.19921875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="50.296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="55.19921875" style="1" customWidth="1"/>
     <col min="6" max="6" width="28.19921875" style="1" customWidth="1"/>
     <col min="7" max="16384" width="8.796875" style="1"/>
   </cols>
@@ -1638,6 +1686,9 @@
       <c r="E30" s="1" t="s">
         <v>110</v>
       </c>
+      <c r="F30" s="1" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1">
@@ -1652,6 +1703,9 @@
       <c r="E31" s="1" t="s">
         <v>120</v>
       </c>
+      <c r="F31" s="1" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1">
@@ -1666,8 +1720,11 @@
       <c r="E32" s="1" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="33" spans="2:5">
+      <c r="F32" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6">
       <c r="B33" s="1">
         <v>30</v>
       </c>
@@ -1680,8 +1737,11 @@
       <c r="E33" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="34" spans="2:5">
+      <c r="F33" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6">
       <c r="B34" s="1">
         <v>31</v>
       </c>
@@ -1694,8 +1754,11 @@
       <c r="E34" s="1" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="35" spans="2:5">
+      <c r="F34" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6">
       <c r="B35" s="1">
         <v>32</v>
       </c>
@@ -1708,8 +1771,11 @@
       <c r="E35" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="36" spans="2:5">
+      <c r="F35" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6">
       <c r="B36" s="1">
         <v>33</v>
       </c>
@@ -1722,8 +1788,11 @@
       <c r="E36" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="37" spans="2:5">
+      <c r="F36" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6">
       <c r="B37" s="1">
         <v>34</v>
       </c>
@@ -1736,8 +1805,11 @@
       <c r="E37" s="1" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="38" spans="2:5">
+      <c r="F37" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6">
       <c r="B38" s="1">
         <v>35</v>
       </c>
@@ -1750,8 +1822,11 @@
       <c r="E38" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="39" spans="2:5">
+      <c r="F38" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6">
       <c r="B39" s="1">
         <v>36</v>
       </c>
@@ -1764,8 +1839,11 @@
       <c r="E39" s="1" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="40" spans="2:5">
+      <c r="F39" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6">
       <c r="B40" s="1">
         <v>37</v>
       </c>
@@ -1778,8 +1856,11 @@
       <c r="E40" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="41" spans="2:5">
+      <c r="F40" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6">
       <c r="B41" s="1">
         <v>38</v>
       </c>
@@ -1792,8 +1873,11 @@
       <c r="E41" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="42" spans="2:5">
+      <c r="F41" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6">
       <c r="B42" s="1">
         <v>39</v>
       </c>
@@ -1806,8 +1890,11 @@
       <c r="E42" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="43" spans="2:5">
+      <c r="F42" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6">
       <c r="B43" s="1">
         <v>40</v>
       </c>
@@ -1820,8 +1907,11 @@
       <c r="E43" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="44" spans="2:5">
+      <c r="F43" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6">
       <c r="B44" s="1">
         <v>41</v>
       </c>
@@ -1834,8 +1924,11 @@
       <c r="E44" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="45" spans="2:5">
+      <c r="F44" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6">
       <c r="B45" s="1">
         <v>42</v>
       </c>
@@ -1848,8 +1941,11 @@
       <c r="E45" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="46" spans="2:5">
+      <c r="F45" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6">
       <c r="B46" s="1">
         <v>43</v>
       </c>
@@ -1862,8 +1958,11 @@
       <c r="E46" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="47" spans="2:5">
+      <c r="F46" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6">
       <c r="B47" s="1">
         <v>44</v>
       </c>
@@ -1876,8 +1975,11 @@
       <c r="E47" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="48" spans="2:5">
+      <c r="F47" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6">
       <c r="B48" s="1">
         <v>45</v>
       </c>
@@ -1890,8 +1992,11 @@
       <c r="E48" s="1" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="49" spans="2:5">
+      <c r="F48" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
       <c r="B49" s="1">
         <v>46</v>
       </c>
@@ -1904,8 +2009,11 @@
       <c r="E49" s="1" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="50" spans="2:5">
+      <c r="F49" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
       <c r="B50" s="1">
         <v>47</v>
       </c>
@@ -1918,8 +2026,11 @@
       <c r="E50" s="1" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="51" spans="2:5">
+      <c r="F50" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="1">
         <v>48</v>
       </c>
@@ -1932,8 +2043,11 @@
       <c r="E51" s="1" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="52" spans="2:5">
+      <c r="F51" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
       <c r="B52" s="1">
         <v>49</v>
       </c>
@@ -1946,8 +2060,11 @@
       <c r="E52" s="1" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="53" spans="2:5">
+      <c r="F52" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6">
       <c r="B53" s="1">
         <v>50</v>
       </c>
@@ -1960,8 +2077,11 @@
       <c r="E53" s="1" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="54" spans="2:5">
+      <c r="F53" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6">
       <c r="B54" s="1">
         <v>51</v>
       </c>
@@ -1974,8 +2094,11 @@
       <c r="E54" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="55" spans="2:5">
+      <c r="F54" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
       <c r="B55" s="1">
         <v>52</v>
       </c>
@@ -1988,8 +2111,11 @@
       <c r="E55" s="1" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="56" spans="2:5">
+      <c r="F55" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
       <c r="B56" s="1">
         <v>53</v>
       </c>
@@ -2002,8 +2128,11 @@
       <c r="E56" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="57" spans="2:5">
+      <c r="F56" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6">
       <c r="B57" s="1">
         <v>54</v>
       </c>
@@ -2016,8 +2145,11 @@
       <c r="E57" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="58" spans="2:5">
+      <c r="F57" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
       <c r="B58" s="1">
         <v>55</v>
       </c>
@@ -2030,8 +2162,11 @@
       <c r="E58" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="59" spans="2:5">
+      <c r="F58" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6">
       <c r="B59" s="1">
         <v>56</v>
       </c>
@@ -2044,8 +2179,11 @@
       <c r="E59" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="60" spans="2:5">
+      <c r="F59" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="1">
         <v>57</v>
       </c>
@@ -2058,8 +2196,11 @@
       <c r="E60" s="1" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="61" spans="2:5">
+      <c r="F60" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
       <c r="B61" s="1">
         <v>58</v>
       </c>
@@ -2072,8 +2213,11 @@
       <c r="E61" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="62" spans="2:5">
+      <c r="F61" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
       <c r="B62" s="1">
         <v>59</v>
       </c>
@@ -2086,8 +2230,11 @@
       <c r="E62" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="63" spans="2:5">
+      <c r="F62" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6">
       <c r="B63" s="1">
         <v>60</v>
       </c>
@@ -2100,8 +2247,11 @@
       <c r="E63" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="64" spans="2:5">
+      <c r="F63" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
       <c r="B64" s="1">
         <v>61</v>
       </c>
@@ -2114,8 +2264,11 @@
       <c r="E64" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="65" spans="2:5">
+      <c r="F64" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6">
       <c r="B65" s="1">
         <v>62</v>
       </c>
@@ -2128,8 +2281,11 @@
       <c r="E65" s="1" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="66" spans="2:5">
+      <c r="F65" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6">
       <c r="B66" s="1">
         <v>63</v>
       </c>
@@ -2142,8 +2298,11 @@
       <c r="E66" s="1" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="67" spans="2:5">
+      <c r="F66" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6">
       <c r="B67" s="1">
         <v>64</v>
       </c>
@@ -2151,7 +2310,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="68" spans="2:5">
+    <row r="68" spans="2:6">
       <c r="B68" s="1">
         <v>65</v>
       </c>
@@ -2159,7 +2318,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="69" spans="2:5">
+    <row r="69" spans="2:6">
       <c r="B69" s="1">
         <v>66</v>
       </c>
@@ -2167,7 +2326,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="70" spans="2:5">
+    <row r="70" spans="2:6">
       <c r="B70" s="1">
         <v>67</v>
       </c>
@@ -2175,7 +2334,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="71" spans="2:5">
+    <row r="71" spans="2:6">
       <c r="B71" s="1">
         <v>68</v>
       </c>
@@ -2183,7 +2342,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="72" spans="2:5">
+    <row r="72" spans="2:6">
       <c r="B72" s="1">
         <v>69</v>
       </c>
@@ -2191,7 +2350,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="73" spans="2:5">
+    <row r="73" spans="2:6">
       <c r="B73" s="1">
         <v>70</v>
       </c>
@@ -2199,7 +2358,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="74" spans="2:5">
+    <row r="74" spans="2:6">
       <c r="B74" s="1">
         <v>71</v>
       </c>
@@ -2207,7 +2366,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="2:5">
+    <row r="75" spans="2:6">
       <c r="B75" s="1">
         <v>72</v>
       </c>
@@ -2215,7 +2374,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="76" spans="2:5">
+    <row r="76" spans="2:6">
       <c r="B76" s="1">
         <v>73</v>
       </c>
@@ -2223,7 +2382,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="77" spans="2:5">
+    <row r="77" spans="2:6">
       <c r="B77" s="1">
         <v>74</v>
       </c>
@@ -2231,7 +2390,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="78" spans="2:5">
+    <row r="78" spans="2:6">
       <c r="B78" s="1">
         <v>75</v>
       </c>
@@ -2239,7 +2398,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="79" spans="2:5">
+    <row r="79" spans="2:6">
       <c r="B79" s="1">
         <v>76</v>
       </c>
@@ -2247,7 +2406,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="80" spans="2:5">
+    <row r="80" spans="2:6">
       <c r="B80" s="1">
         <v>77</v>
       </c>

--- a/Jpn_test/doc/テスト結果.xlsx
+++ b/Jpn_test/doc/テスト結果.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Acucorp\acutest\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ISTEST\Git\Jpn_test\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E326D36-440C-4F1E-A7F5-78E3A652E2E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C117366F-D56C-4C7F-A205-2AA9A03CACE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="153">
   <si>
     <t>CS-01</t>
   </si>
@@ -581,19 +581,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>NG(実行時NB0/組み合わせエラー）</t>
-    <rPh sb="3" eb="6">
-      <t>ジッコウジ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ク</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>NG（コンパイル時エラー）</t>
     <rPh sb="8" eb="9">
       <t>ジ</t>
@@ -601,16 +588,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>NG(実行時JUST、SPACE、ALL定数、１B-＞２Bエラー）</t>
-    <rPh sb="3" eb="6">
-      <t>ジッコウジ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>テイスウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>NG（コンパイル時エラーならない、QUOTESとZEROS比較）</t>
     <rPh sb="8" eb="9">
       <t>ジ</t>
@@ -887,6 +864,26 @@
   </si>
   <si>
     <t>NG(BYTE-LENGTHなし）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（1B→2B変換されない、JUST効かない）</t>
+    <rPh sb="8" eb="10">
+      <t>ヘンカン</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG(実行時NBN,N/N,N0N,編集効かないエラー）</t>
+    <rPh sb="3" eb="6">
+      <t>ジッコウジ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>ヘンシュウキ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -917,12 +914,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -937,9 +940,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1547,8 +1551,8 @@
       <c r="D22" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>99</v>
+      <c r="E22" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>82</v>
@@ -1615,11 +1619,11 @@
       <c r="D26" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -1649,11 +1653,8 @@
       <c r="D28" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>119</v>
+      <c r="E28" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="2:6">
@@ -1681,7 +1682,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>110</v>
@@ -1698,13 +1699,13 @@
         <v>26</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="2:6">
@@ -1715,13 +1716,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="2:6">
@@ -1732,7 +1733,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>110</v>
@@ -1749,13 +1750,10 @@
         <v>29</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>147</v>
+        <v>120</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="2:6">
@@ -1766,13 +1764,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="2:6">
@@ -1783,7 +1781,7 @@
         <v>31</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>110</v>
@@ -1800,10 +1798,10 @@
         <v>32</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>110</v>
@@ -1817,7 +1815,7 @@
         <v>33</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>110</v>
@@ -1834,13 +1832,13 @@
         <v>34</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="40" spans="2:6">
@@ -1851,13 +1849,13 @@
         <v>35</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41" spans="2:6">
@@ -1868,10 +1866,10 @@
         <v>36</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>82</v>
@@ -1885,10 +1883,10 @@
         <v>37</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>82</v>
@@ -1902,7 +1900,7 @@
         <v>38</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>110</v>
@@ -1919,10 +1917,10 @@
         <v>39</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>82</v>
@@ -1936,7 +1934,7 @@
         <v>40</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>110</v>
@@ -1953,13 +1951,13 @@
         <v>41</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="2:6">
@@ -1970,13 +1968,13 @@
         <v>42</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="2:6">
@@ -1987,13 +1985,13 @@
         <v>43</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="F48" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -2004,10 +2002,10 @@
         <v>44</v>
       </c>
       <c r="D49" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>116</v>
@@ -2021,13 +2019,13 @@
         <v>45</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="51" spans="2:6">
@@ -2038,13 +2036,13 @@
         <v>46</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52" spans="2:6">
@@ -2055,13 +2053,13 @@
         <v>47</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="53" spans="2:6">
@@ -2072,13 +2070,13 @@
         <v>48</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="54" spans="2:6">
@@ -2089,7 +2087,7 @@
         <v>49</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>82</v>
@@ -2106,10 +2104,10 @@
         <v>50</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>116</v>
@@ -2123,13 +2121,13 @@
         <v>51</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" spans="2:6">
@@ -2140,7 +2138,7 @@
         <v>52</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>110</v>
@@ -2157,13 +2155,13 @@
         <v>53</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="59" spans="2:6">
@@ -2174,7 +2172,7 @@
         <v>54</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>110</v>
@@ -2191,13 +2189,13 @@
         <v>55</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61" spans="2:6">
@@ -2208,13 +2206,13 @@
         <v>56</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="62" spans="2:6">
@@ -2225,7 +2223,7 @@
         <v>57</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>110</v>
@@ -2242,13 +2240,13 @@
         <v>58</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -2259,7 +2257,7 @@
         <v>59</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>110</v>
@@ -2276,13 +2274,13 @@
         <v>60</v>
       </c>
       <c r="D65" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="F65" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -2293,13 +2291,13 @@
         <v>61</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="67" spans="2:6">

--- a/Jpn_test/doc/テスト結果.xlsx
+++ b/Jpn_test/doc/テスト結果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ISTEST\Git\Jpn_test\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C117366F-D56C-4C7F-A205-2AA9A03CACE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2E2F86-F681-4B00-A8A3-09E5D34B0916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="154">
   <si>
     <t>CS-01</t>
   </si>
@@ -621,16 +621,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>NG（SPACE、ZEROとの比較一致しない）</t>
-    <rPh sb="15" eb="17">
-      <t>ヒカク</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>イッチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>条件名</t>
     <rPh sb="0" eb="3">
       <t>ジョウケンメイ</t>
@@ -883,6 +873,26 @@
     </rPh>
     <rPh sb="18" eb="21">
       <t>ヘンシュウキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（VALUEはMOVEと同じ：is)</t>
+    <rPh sb="14" eb="15">
+      <t>オナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG（SPACE、ZERO、QUOTESとの大小比較一致しない）</t>
+    <rPh sb="22" eb="24">
+      <t>ダイショウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヒカク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>イッチ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1552,7 +1562,7 @@
         <v>108</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>82</v>
@@ -1620,7 +1630,7 @@
         <v>113</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>117</v>
@@ -1656,6 +1666,9 @@
       <c r="E28" s="2" t="s">
         <v>99</v>
       </c>
+      <c r="F28" s="1" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1">
@@ -1705,7 +1718,7 @@
         <v>118</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="2:6">
@@ -1722,7 +1735,7 @@
         <v>118</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33" spans="2:6">
@@ -1753,7 +1766,7 @@
         <v>120</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>121</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35" spans="2:6">
@@ -1770,7 +1783,7 @@
         <v>82</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" spans="2:6">
@@ -1798,10 +1811,10 @@
         <v>32</v>
       </c>
       <c r="D37" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>110</v>
@@ -1815,7 +1828,7 @@
         <v>33</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>110</v>
@@ -1832,13 +1845,13 @@
         <v>34</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="F39" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="2:6">
@@ -1849,13 +1862,13 @@
         <v>35</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="2:6">
@@ -1866,10 +1879,10 @@
         <v>36</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>82</v>
@@ -1883,10 +1896,10 @@
         <v>37</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>82</v>
@@ -1900,7 +1913,7 @@
         <v>38</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>110</v>
@@ -1917,10 +1930,10 @@
         <v>39</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>82</v>
@@ -1934,7 +1947,7 @@
         <v>40</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>110</v>
@@ -1951,13 +1964,13 @@
         <v>41</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47" spans="2:6">
@@ -1968,13 +1981,13 @@
         <v>42</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="2:6">
@@ -1985,13 +1998,13 @@
         <v>43</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -2002,10 +2015,10 @@
         <v>44</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>116</v>
@@ -2019,13 +2032,13 @@
         <v>45</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="2:6">
@@ -2036,13 +2049,13 @@
         <v>46</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52" spans="2:6">
@@ -2053,13 +2066,13 @@
         <v>47</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="F52" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53" spans="2:6">
@@ -2070,13 +2083,13 @@
         <v>48</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54" spans="2:6">
@@ -2087,7 +2100,7 @@
         <v>49</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>82</v>
@@ -2104,10 +2117,10 @@
         <v>50</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>116</v>
@@ -2121,13 +2134,13 @@
         <v>51</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="2:6">
@@ -2138,7 +2151,7 @@
         <v>52</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>110</v>
@@ -2155,13 +2168,13 @@
         <v>53</v>
       </c>
       <c r="D58" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="F58" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="59" spans="2:6">
@@ -2172,7 +2185,7 @@
         <v>54</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>110</v>
@@ -2189,13 +2202,13 @@
         <v>55</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61" spans="2:6">
@@ -2206,13 +2219,13 @@
         <v>56</v>
       </c>
       <c r="D61" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E61" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="F61" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="62" spans="2:6">
@@ -2223,7 +2236,7 @@
         <v>57</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>110</v>
@@ -2240,13 +2253,13 @@
         <v>58</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -2257,7 +2270,7 @@
         <v>59</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>110</v>
@@ -2274,13 +2287,13 @@
         <v>60</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -2291,13 +2304,13 @@
         <v>61</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="F66" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="67" spans="2:6">
